--- a/research/traditional_assets/database/data/kenya/kenya_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07439999999999999</v>
+        <v>0.0682</v>
       </c>
       <c r="E2">
-        <v>-0.004759999999999999</v>
+        <v>-0.12285</v>
       </c>
       <c r="G2">
-        <v>-0.01316653458621081</v>
+        <v>0.09440008631851532</v>
       </c>
       <c r="H2">
-        <v>-0.01316653458621081</v>
+        <v>0.09440008631851532</v>
       </c>
       <c r="I2">
-        <v>-0.0215442092154421</v>
+        <v>0.0790677600345274</v>
       </c>
       <c r="J2">
-        <v>-0.01886668602248837</v>
+        <v>0.04947788253765551</v>
       </c>
       <c r="K2">
-        <v>-19.587</v>
+        <v>52.706</v>
       </c>
       <c r="L2">
-        <v>-0.02217479904902072</v>
+        <v>0.05686879585671126</v>
       </c>
       <c r="M2">
-        <v>11.964</v>
+        <v>5.19</v>
       </c>
       <c r="N2">
-        <v>0.02634081902245707</v>
+        <v>0.01798336798336798</v>
       </c>
       <c r="O2">
-        <v>-0.6108132945320874</v>
+        <v>0.09847076234204835</v>
       </c>
       <c r="P2">
-        <v>11.964</v>
+        <v>5.19</v>
       </c>
       <c r="Q2">
-        <v>0.02634081902245707</v>
+        <v>0.01798336798336798</v>
       </c>
       <c r="R2">
-        <v>-0.6108132945320874</v>
+        <v>0.09847076234204835</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>212.67</v>
+        <v>56.38</v>
       </c>
       <c r="V2">
-        <v>0.4682298546895641</v>
-      </c>
-      <c r="W2">
-        <v>0.03751619047951007</v>
+        <v>0.1953568953568953</v>
       </c>
       <c r="X2">
-        <v>0.09075037096995152</v>
-      </c>
-      <c r="Y2">
-        <v>-0.05323418049044145</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="Z2">
-        <v>1.647087342433058</v>
-      </c>
-      <c r="AA2">
-        <v>0.07250350194235097</v>
+        <v>2.554575523704521</v>
       </c>
       <c r="AB2">
-        <v>0.08536318360626029</v>
-      </c>
-      <c r="AC2">
-        <v>-0.0142893986198506</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD2">
-        <v>87.211</v>
+        <v>38.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>87.211</v>
+        <v>38.7</v>
       </c>
       <c r="AG2">
-        <v>-125.459</v>
+        <v>-17.68</v>
       </c>
       <c r="AH2">
-        <v>0.1610809532868745</v>
+        <v>0.1182401466544455</v>
       </c>
       <c r="AI2">
-        <v>0.1144184484348822</v>
+        <v>0.07961324830281835</v>
       </c>
       <c r="AJ2">
-        <v>-0.3816347823970846</v>
+        <v>-0.06525911708253358</v>
       </c>
       <c r="AK2">
-        <v>-0.2282977976165563</v>
+        <v>-0.04114306990598529</v>
       </c>
       <c r="AL2">
-        <v>4.423</v>
+        <v>8.087</v>
       </c>
       <c r="AM2">
-        <v>4.103</v>
+        <v>8.087</v>
       </c>
       <c r="AN2">
-        <v>-7.786696428571424</v>
+        <v>0.5020757654385055</v>
       </c>
       <c r="AO2">
-        <v>-4.302509608862763</v>
+        <v>9.061456658835167</v>
       </c>
       <c r="AP2">
-        <v>11.20169642857142</v>
+        <v>-0.2293720809548521</v>
       </c>
       <c r="AQ2">
-        <v>-4.638069705093836</v>
+        <v>9.061456658835167</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liberty Kenya Holdings Plc (NASE:LBTY)</t>
+          <t>Britam Holdings Plc (NASE:BRIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,28 +710,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0428</v>
+        <v>0.137</v>
       </c>
       <c r="E3">
-        <v>-0.004759999999999999</v>
+        <v>-0.5479999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1179713340683572</v>
+        <v>0.04512126339537507</v>
       </c>
       <c r="H3">
-        <v>0.1179713340683572</v>
+        <v>0.04512126339537507</v>
       </c>
       <c r="I3">
-        <v>0.1124586549062844</v>
+        <v>0.04060913705583756</v>
       </c>
       <c r="J3">
-        <v>0.07281580270605656</v>
+        <v>0.02030456852791878</v>
       </c>
       <c r="K3">
-        <v>6.04</v>
+        <v>0.408</v>
       </c>
       <c r="L3">
-        <v>0.06659316427783903</v>
+        <v>0.001150592216582064</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +755,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>52.5</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.586102719033233</v>
-      </c>
-      <c r="W3">
-        <v>0.07936925098554534</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.08419474076941814</v>
-      </c>
-      <c r="Y3">
-        <v>-0.004825489783872802</v>
-      </c>
-      <c r="Z3">
-        <v>4.282341831916904</v>
-      </c>
-      <c r="AA3">
-        <v>0.3118221579527541</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AB3">
-        <v>0.0833989401813548</v>
-      </c>
-      <c r="AC3">
-        <v>0.2284232177713993</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD3">
-        <v>0.911</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.911</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-51.589</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.02678545176560524</v>
-      </c>
-      <c r="AI3">
-        <v>0.01130118718289067</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>2.79025366434096</v>
-      </c>
-      <c r="AK3">
-        <v>-1.835189071893564</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.113</v>
+        <v>3.66</v>
       </c>
       <c r="AM3">
-        <v>0.113</v>
+        <v>3.66</v>
       </c>
       <c r="AN3">
-        <v>0.08514018691588786</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>90.26548672566371</v>
+        <v>3.934426229508197</v>
       </c>
       <c r="AP3">
-        <v>-4.821401869158879</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>90.26548672566371</v>
+        <v>3.934426229508197</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +811,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jubilee Holdings Limited (NASE:JUB)</t>
+          <t>Liberty Kenya Holdings Plc (NASE:LBTY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,74 +819,62 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0421</v>
+      </c>
+      <c r="E4">
+        <v>-0.328</v>
+      </c>
       <c r="G4">
-        <v>0.1031259129418639</v>
+        <v>0.03533678756476684</v>
       </c>
       <c r="H4">
-        <v>0.1031259129418639</v>
+        <v>0.03533678756476684</v>
       </c>
       <c r="I4">
-        <v>0.1063394683026585</v>
+        <v>0.03025906735751295</v>
       </c>
       <c r="J4">
-        <v>0.09096159157676244</v>
+        <v>0.01512953367875648</v>
       </c>
       <c r="K4">
-        <v>58.4</v>
+        <v>0.708</v>
       </c>
       <c r="L4">
-        <v>0.170610575518551</v>
+        <v>0.007336787564766839</v>
       </c>
       <c r="M4">
-        <v>6.09</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03002958579881657</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.1042808219178082</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>6.09</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03002958579881657</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1042808219178082</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.4339250493096647</v>
-      </c>
-      <c r="W4">
-        <v>0.2094691535150645</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.08288873247043339</v>
-      </c>
-      <c r="Y4">
-        <v>0.1265804210446311</v>
-      </c>
-      <c r="Z4">
-        <v>2.060806742925948</v>
-      </c>
-      <c r="AA4">
-        <v>0.1874542612686682</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AB4">
-        <v>0.08288873247043339</v>
-      </c>
-      <c r="AC4">
-        <v>0.1045655287982348</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -931,37 +886,31 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-88</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
       <c r="AJ4">
-        <v>-0.7665505226480835</v>
-      </c>
-      <c r="AK4">
-        <v>-0.3136136849607983</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="AM4">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>36.4</v>
+        <v>30.73684210526316</v>
       </c>
       <c r="AP4">
-        <v>-2.391304347826087</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>36.4</v>
+        <v>30.73684210526316</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +921,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIC Insurance Group Plc (NASE:CIC)</t>
+          <t>Jubilee Holdings Limited (NASE:JUB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -980,41 +929,47 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.0568</v>
+      </c>
+      <c r="E5">
+        <v>0.0823</v>
+      </c>
       <c r="G5">
-        <v>0.006815286624203822</v>
+        <v>0.1895994832041344</v>
       </c>
       <c r="H5">
-        <v>0.006815286624203822</v>
+        <v>0.1895994832041344</v>
       </c>
       <c r="I5">
-        <v>-0.03203821656050956</v>
+        <v>0.1521317829457364</v>
       </c>
       <c r="J5">
-        <v>-0.03203821656050956</v>
+        <v>0.1186529439803316</v>
       </c>
       <c r="K5">
-        <v>-0.327</v>
+        <v>45.6</v>
       </c>
       <c r="L5">
-        <v>-0.002082802547770701</v>
+        <v>0.1472868217054263</v>
       </c>
       <c r="M5">
-        <v>0.104</v>
+        <v>5.19</v>
       </c>
       <c r="N5">
-        <v>0.002035225048923679</v>
+        <v>0.04447300771208226</v>
       </c>
       <c r="O5">
-        <v>-0.3180428134556575</v>
+        <v>0.1138157894736842</v>
       </c>
       <c r="P5">
-        <v>0.104</v>
+        <v>5.19</v>
       </c>
       <c r="Q5">
-        <v>0.002035225048923679</v>
+        <v>0.04447300771208226</v>
       </c>
       <c r="R5">
-        <v>-0.3180428134556575</v>
+        <v>0.1138157894736842</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,64 +978,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.57</v>
+        <v>54.6</v>
       </c>
       <c r="V5">
-        <v>0.06986301369863013</v>
+        <v>0.467866323907455</v>
       </c>
       <c r="W5">
-        <v>-0.004336870026525199</v>
+        <v>0.1337635670284541</v>
       </c>
       <c r="X5">
-        <v>0.1158544859320825</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="Y5">
-        <v>-0.1201913559586077</v>
+        <v>0.0006699297937033943</v>
       </c>
       <c r="Z5">
-        <v>1.324894514767933</v>
+        <v>1.224199288256228</v>
       </c>
       <c r="AA5">
-        <v>-0.04244725738396625</v>
+        <v>0.1452548495702281</v>
       </c>
       <c r="AB5">
-        <v>0.09069706865396975</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AC5">
-        <v>-0.133144326037936</v>
+        <v>0.01216121233547737</v>
       </c>
       <c r="AD5">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>31.93</v>
+        <v>-54.6</v>
       </c>
       <c r="AH5">
-        <v>0.4099307159353349</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.3349056603773585</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.3845597976634951</v>
+        <v>-0.8792270531400966</v>
       </c>
       <c r="AK5">
-        <v>0.3117250805428097</v>
+        <v>-0.167741935483871</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.922</v>
       </c>
       <c r="AM5">
-        <v>-0.32</v>
+        <v>0.922</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>51.08459869848156</v>
+      </c>
+      <c r="AP5">
+        <v>-1.1375</v>
       </c>
       <c r="AQ5">
-        <v>15.71875</v>
+        <v>51.08459869848156</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1055,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Britam Holdings Plc (NASE:BRIT)</t>
+          <t>CIC Insurance Group Plc (NASE:CIC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,118 +1064,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.106</v>
+        <v>0.0796</v>
+      </c>
+      <c r="E6">
+        <v>0.342</v>
       </c>
       <c r="G6">
-        <v>-0.2001363791339925</v>
+        <v>0.05647200481637568</v>
       </c>
       <c r="H6">
-        <v>-0.2001363791339925</v>
+        <v>0.05647200481637568</v>
       </c>
       <c r="I6">
-        <v>-0.2066143879986362</v>
+        <v>0.05334136062612883</v>
       </c>
       <c r="J6">
-        <v>-0.2066143879986362</v>
+        <v>0.03857257999674463</v>
       </c>
       <c r="K6">
-        <v>-83.7</v>
+        <v>5.99</v>
       </c>
       <c r="L6">
-        <v>-0.2853733378793045</v>
+        <v>0.03606261288380494</v>
       </c>
       <c r="M6">
-        <v>5.77</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03450956937799043</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.06893667861409797</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>5.77</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03450956937799043</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0.06893667861409797</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>68.59999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="V6">
-        <v>0.4102870813397129</v>
+        <v>0.04309927360774819</v>
       </c>
       <c r="W6">
-        <v>-0.2895191975095123</v>
+        <v>0.08544935805991442</v>
       </c>
       <c r="X6">
-        <v>0.09730600117048489</v>
+        <v>0.1949438704717821</v>
       </c>
       <c r="Y6">
-        <v>-0.3868251986799972</v>
+        <v>-0.1094945124118677</v>
       </c>
       <c r="Z6">
-        <v>1.272451193058568</v>
+        <v>1.511373976342129</v>
       </c>
       <c r="AA6">
-        <v>-0.2629067245119305</v>
+        <v>0.05829759360745482</v>
       </c>
       <c r="AB6">
-        <v>0.08732742703116578</v>
+        <v>0.1433410069613328</v>
       </c>
       <c r="AC6">
-        <v>-0.3502341515430963</v>
+        <v>-0.08504341335387794</v>
       </c>
       <c r="AD6">
-        <v>50.8</v>
+        <v>38.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>50.8</v>
+        <v>38.7</v>
       </c>
       <c r="AG6">
-        <v>-17.8</v>
+        <v>36.92</v>
       </c>
       <c r="AH6">
-        <v>0.2330275229357798</v>
+        <v>0.48375</v>
       </c>
       <c r="AI6">
-        <v>0.2454106280193236</v>
+        <v>0.3650943396226415</v>
       </c>
       <c r="AJ6">
-        <v>-0.1191432396251673</v>
+        <v>0.4720020455126566</v>
       </c>
       <c r="AK6">
-        <v>-0.1286127167630058</v>
+        <v>0.3542506236806755</v>
       </c>
       <c r="AL6">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="AM6">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="AN6">
-        <v>-0.8654173764906302</v>
+        <v>4.002068252326784</v>
       </c>
       <c r="AO6">
-        <v>-18.30815709969789</v>
+        <v>2.598240469208211</v>
       </c>
       <c r="AP6">
-        <v>0.3032367972742759</v>
+        <v>3.81799379524302</v>
       </c>
       <c r="AQ6">
-        <v>-18.30815709969789</v>
+        <v>2.598240469208211</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0682</v>
+        <v>0.0411</v>
       </c>
       <c r="E2">
-        <v>-0.12285</v>
+        <v>0.137</v>
       </c>
       <c r="G2">
-        <v>0.09440008631851532</v>
+        <v>0.07477283596365375</v>
       </c>
       <c r="H2">
-        <v>0.09440008631851532</v>
+        <v>0.07477283596365375</v>
       </c>
       <c r="I2">
-        <v>0.0790677600345274</v>
+        <v>0.07529890004782401</v>
       </c>
       <c r="J2">
-        <v>0.04947788253765551</v>
+        <v>0.04845039187527686</v>
       </c>
       <c r="K2">
-        <v>52.706</v>
+        <v>78</v>
       </c>
       <c r="L2">
-        <v>0.05686879585671126</v>
+        <v>0.09325681492109039</v>
       </c>
       <c r="M2">
-        <v>5.19</v>
+        <v>5.28</v>
       </c>
       <c r="N2">
-        <v>0.01798336798336798</v>
+        <v>0.02481203007518797</v>
       </c>
       <c r="O2">
-        <v>0.09847076234204835</v>
+        <v>0.06769230769230769</v>
       </c>
       <c r="P2">
-        <v>5.19</v>
+        <v>5.28</v>
       </c>
       <c r="Q2">
-        <v>0.01798336798336798</v>
+        <v>0.02481203007518797</v>
       </c>
       <c r="R2">
-        <v>0.09847076234204835</v>
+        <v>0.06769230769230769</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>56.38</v>
+        <v>117.99</v>
       </c>
       <c r="V2">
-        <v>0.1953568953568953</v>
+        <v>0.5544642857142857</v>
+      </c>
+      <c r="W2">
+        <v>0.1537668531267929</v>
       </c>
       <c r="X2">
-        <v>0.1330936372347507</v>
+        <v>0.1417063275567617</v>
+      </c>
+      <c r="Y2">
+        <v>0.01206052557003123</v>
       </c>
       <c r="Z2">
-        <v>2.554575523704521</v>
+        <v>1.544826567175206</v>
+      </c>
+      <c r="AA2">
+        <v>0.09489841023538634</v>
       </c>
       <c r="AB2">
-        <v>0.1330936372347507</v>
+        <v>0.129681599875213</v>
+      </c>
+      <c r="AC2">
+        <v>-0.03752202261912974</v>
       </c>
       <c r="AD2">
-        <v>38.7</v>
+        <v>73.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>38.7</v>
+        <v>73.3</v>
       </c>
       <c r="AG2">
-        <v>-17.68</v>
+        <v>-44.69</v>
       </c>
       <c r="AH2">
-        <v>0.1182401466544455</v>
+        <v>0.2562041244320168</v>
       </c>
       <c r="AI2">
-        <v>0.07961324830281835</v>
+        <v>0.1056805074971165</v>
       </c>
       <c r="AJ2">
-        <v>-0.06525911708253358</v>
+        <v>-0.2658378442686337</v>
       </c>
       <c r="AK2">
-        <v>-0.04114306990598529</v>
+        <v>-0.07763937388162122</v>
       </c>
       <c r="AL2">
-        <v>8.087</v>
+        <v>6.827</v>
       </c>
       <c r="AM2">
-        <v>8.087</v>
+        <v>6.827</v>
       </c>
       <c r="AN2">
-        <v>0.5020757654385055</v>
+        <v>1.1149984788561</v>
       </c>
       <c r="AO2">
-        <v>9.061456658835167</v>
+        <v>9.225135491431082</v>
       </c>
       <c r="AP2">
-        <v>-0.2293720809548521</v>
+        <v>-0.6797992090051719</v>
       </c>
       <c r="AQ2">
-        <v>9.061456658835167</v>
+        <v>9.225135491431082</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Britam Holdings Plc (NASE:BRIT)</t>
+          <t>Liberty Kenya Holdings Plc (NASE:LBTY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.137</v>
+        <v>0.00063</v>
       </c>
       <c r="E3">
-        <v>-0.5479999999999999</v>
+        <v>-0.126</v>
       </c>
       <c r="G3">
-        <v>0.04512126339537507</v>
+        <v>0.07122641509433962</v>
       </c>
       <c r="H3">
-        <v>0.04512126339537507</v>
+        <v>0.07122641509433962</v>
       </c>
       <c r="I3">
-        <v>0.04060913705583756</v>
+        <v>0.06462264150943398</v>
       </c>
       <c r="J3">
-        <v>0.02030456852791878</v>
+        <v>0.03680733013617112</v>
       </c>
       <c r="K3">
-        <v>0.408</v>
+        <v>2.7</v>
       </c>
       <c r="L3">
-        <v>0.001150592216582064</v>
+        <v>0.03183962264150943</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1330936372347507</v>
+        <v>0.1266039965181308</v>
       </c>
       <c r="AB3">
-        <v>0.1330936372347507</v>
+        <v>0.1266039965181308</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -785,22 +797,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>3.66</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AM3">
-        <v>3.66</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>3.934426229508197</v>
+        <v>62.98850574712645</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>3.934426229508197</v>
+        <v>62.98850574712645</v>
       </c>
     </row>
     <row r="4">
@@ -811,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liberty Kenya Holdings Plc (NASE:LBTY)</t>
+          <t>The CIC Insurance Group Plc (NASE:CIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -820,28 +832,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0421</v>
+        <v>0.0934</v>
       </c>
       <c r="E4">
-        <v>-0.328</v>
+        <v>0.172</v>
       </c>
       <c r="G4">
-        <v>0.03533678756476684</v>
+        <v>0.09001731102135026</v>
       </c>
       <c r="H4">
-        <v>0.03533678756476684</v>
+        <v>0.09001731102135026</v>
       </c>
       <c r="I4">
-        <v>0.03025906735751295</v>
+        <v>0.1067512983266013</v>
       </c>
       <c r="J4">
-        <v>0.01512953367875648</v>
+        <v>0.05963911819776958</v>
       </c>
       <c r="K4">
-        <v>0.708</v>
+        <v>10.7</v>
       </c>
       <c r="L4">
-        <v>0.007336787564766839</v>
+        <v>0.06174264281592613</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,52 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.09331550802139038</v>
+      </c>
+      <c r="W4">
+        <v>0.1592261904761905</v>
       </c>
       <c r="X4">
-        <v>0.1330936372347507</v>
+        <v>0.1826436060605849</v>
+      </c>
+      <c r="Y4">
+        <v>-0.02341741558439439</v>
+      </c>
+      <c r="Z4">
+        <v>1.664425662696888</v>
+      </c>
+      <c r="AA4">
+        <v>0.09926487882898069</v>
       </c>
       <c r="AB4">
-        <v>0.1330936372347507</v>
+        <v>0.1342133013521379</v>
+      </c>
+      <c r="AC4">
+        <v>-0.03494842252315716</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>34.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>34.1</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>30.61</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.4769230769230769</v>
+      </c>
+      <c r="AI4">
+        <v>0.3537344398340249</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>0.4500808704602265</v>
+      </c>
+      <c r="AK4">
+        <v>0.3294586158648154</v>
       </c>
       <c r="AL4">
-        <v>0.095</v>
+        <v>3.31</v>
       </c>
       <c r="AM4">
-        <v>0.095</v>
+        <v>3.31</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.813829787234043</v>
       </c>
       <c r="AO4">
-        <v>30.73684210526316</v>
+        <v>5.589123867069486</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.628191489361702</v>
       </c>
       <c r="AQ4">
-        <v>30.73684210526316</v>
+        <v>5.589123867069486</v>
       </c>
     </row>
     <row r="5">
@@ -921,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jubilee Holdings Limited (NASE:JUB)</t>
+          <t>Britam Holdings Plc (NASE:BRIT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -930,121 +963,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0568</v>
+        <v>0.0645</v>
       </c>
       <c r="E5">
-        <v>0.0823</v>
+        <v>0.253</v>
       </c>
       <c r="G5">
-        <v>0.1895994832041344</v>
+        <v>0.07206317867719644</v>
       </c>
       <c r="H5">
-        <v>0.1895994832041344</v>
+        <v>0.07206317867719644</v>
       </c>
       <c r="I5">
-        <v>0.1521317829457364</v>
+        <v>0.06745640013162225</v>
       </c>
       <c r="J5">
-        <v>0.1186529439803316</v>
+        <v>0.03866747622607636</v>
       </c>
       <c r="K5">
-        <v>45.6</v>
+        <v>12.9</v>
       </c>
       <c r="L5">
-        <v>0.1472868217054263</v>
+        <v>0.0424481737413623</v>
       </c>
       <c r="M5">
-        <v>5.19</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04447300771208226</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1138157894736842</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>5.19</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.04447300771208226</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1138157894736842</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>54.6</v>
+        <v>64.7</v>
       </c>
       <c r="V5">
-        <v>0.467866323907455</v>
+        <v>0.8391699092088198</v>
       </c>
       <c r="W5">
-        <v>0.1337635670284541</v>
+        <v>0.07710699342498506</v>
       </c>
       <c r="X5">
-        <v>0.1330936372347507</v>
+        <v>0.1473307505600242</v>
       </c>
       <c r="Y5">
-        <v>0.0006699297937033943</v>
+        <v>-0.07022375713503914</v>
       </c>
       <c r="Z5">
-        <v>1.224199288256228</v>
+        <v>2.341294298921417</v>
       </c>
       <c r="AA5">
-        <v>0.1452548495702281</v>
+        <v>0.09053194164179199</v>
       </c>
       <c r="AB5">
-        <v>0.1330936372347507</v>
+        <v>0.1306275643568943</v>
       </c>
       <c r="AC5">
-        <v>0.01216121233547737</v>
+        <v>-0.04009562271510231</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG5">
-        <v>-54.6</v>
+        <v>-38.7</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.2521823472356935</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.1334017444843509</v>
       </c>
       <c r="AJ5">
-        <v>-0.8792270531400966</v>
+        <v>-1.0078125</v>
       </c>
       <c r="AK5">
-        <v>-0.167741935483871</v>
+        <v>-0.2972350230414747</v>
       </c>
       <c r="AL5">
-        <v>0.922</v>
+        <v>2.21</v>
       </c>
       <c r="AM5">
-        <v>0.922</v>
+        <v>2.21</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.187214611872146</v>
       </c>
       <c r="AO5">
-        <v>51.08459869848156</v>
+        <v>9.276018099547512</v>
       </c>
       <c r="AP5">
-        <v>-1.1375</v>
+        <v>-1.767123287671233</v>
       </c>
       <c r="AQ5">
-        <v>51.08459869848156</v>
+        <v>9.276018099547512</v>
       </c>
     </row>
     <row r="6">
@@ -1055,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIC Insurance Group Plc (NASE:CIC)</t>
+          <t>Jubilee Holdings Limited (NASE:JUB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1064,118 +1094,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0796</v>
+        <v>0.0177</v>
       </c>
       <c r="E6">
-        <v>0.342</v>
+        <v>0.102</v>
       </c>
       <c r="G6">
-        <v>0.05647200481637568</v>
+        <v>0.06924198250728864</v>
       </c>
       <c r="H6">
-        <v>0.05647200481637568</v>
+        <v>0.06924198250728864</v>
       </c>
       <c r="I6">
-        <v>0.05334136062612883</v>
+        <v>0.0674198250728863</v>
       </c>
       <c r="J6">
-        <v>0.03857257999674463</v>
+        <v>0.05880998183816852</v>
       </c>
       <c r="K6">
-        <v>5.99</v>
+        <v>51.7</v>
       </c>
       <c r="L6">
-        <v>0.03606261288380494</v>
+        <v>0.1884110787172012</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>5.28</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.06168224299065421</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.1021276595744681</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>5.28</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.06168224299065421</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1021276595744681</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>1.78</v>
+        <v>49.8</v>
       </c>
       <c r="V6">
-        <v>0.04309927360774819</v>
+        <v>0.5817757009345794</v>
       </c>
       <c r="W6">
-        <v>0.08544935805991442</v>
+        <v>0.1483075157773953</v>
       </c>
       <c r="X6">
-        <v>0.1949438704717821</v>
+        <v>0.1360819045534991</v>
       </c>
       <c r="Y6">
-        <v>-0.1094945124118677</v>
+        <v>0.01222561122389615</v>
       </c>
       <c r="Z6">
-        <v>1.511373976342129</v>
+        <v>0.8923577235772358</v>
       </c>
       <c r="AA6">
-        <v>0.05829759360745482</v>
+        <v>0.05247954151672665</v>
       </c>
       <c r="AB6">
-        <v>0.1433410069613328</v>
+        <v>0.1287356353935318</v>
       </c>
       <c r="AC6">
-        <v>-0.08504341335387794</v>
+        <v>-0.07625609387680513</v>
       </c>
       <c r="AD6">
-        <v>38.7</v>
+        <v>13.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>38.7</v>
+        <v>13.2</v>
       </c>
       <c r="AG6">
-        <v>36.92</v>
+        <v>-36.59999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.48375</v>
+        <v>0.1336032388663967</v>
       </c>
       <c r="AI6">
-        <v>0.3650943396226415</v>
+        <v>0.03281133482475764</v>
       </c>
       <c r="AJ6">
-        <v>0.4720020455126566</v>
+        <v>-0.7469387755102039</v>
       </c>
       <c r="AK6">
-        <v>0.3542506236806755</v>
+        <v>-0.1038297872340425</v>
       </c>
       <c r="AL6">
-        <v>3.41</v>
+        <v>1.22</v>
       </c>
       <c r="AM6">
-        <v>3.41</v>
+        <v>1.22</v>
       </c>
       <c r="AN6">
-        <v>4.002068252326784</v>
+        <v>0.6947368421052631</v>
       </c>
       <c r="AO6">
-        <v>2.598240469208211</v>
+        <v>15.16393442622951</v>
       </c>
       <c r="AP6">
-        <v>3.81799379524302</v>
+        <v>-1.926315789473684</v>
       </c>
       <c r="AQ6">
-        <v>2.598240469208211</v>
+        <v>15.16393442622951</v>
       </c>
     </row>
   </sheetData>
